--- a/outputs/marine_equipment/Остатки_Питер_по_группам.xlsx
+++ b/outputs/marine_equipment/Остатки_Питер_по_группам.xlsx
@@ -10,7 +10,8 @@
     <sheet name="По группам" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Сводка по группам" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Выделенные позиции" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Расхождения и вопросы" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Без чертежа" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Расхождения и вопросы" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'По группам'!$A$4:$Q$138</definedName>
@@ -67,7 +68,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -92,6 +93,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -126,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -155,13 +161,16 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -546,7 +555,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="54" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
@@ -570,7 +579,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Приложения 2 и 3 сведены вместе. Внутри группы — от меньшего диаметра к большему. Желтым помечены титан, высокое давление, котельная арматура, педальные и электромагнитные клапаны.</t>
+          <t>Приложения 2 и 3 сведены вместе. Внутри группы — от меньшего диаметра к большему. Чертеж стоит напротив каждой позиции; где его нет, ячейка желтая — впишите руками. Оранжевым помечены титан, высокое давление, котельная арматура, педальные и электромагнитные.</t>
         </is>
       </c>
     </row>
@@ -602,7 +611,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Обозначение</t>
+          <t>Чертеж</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -2249,7 +2258,7 @@
           <t>Клапан муфтовый проходной запорный Ду20Ру16</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr"/>
+      <c r="F31" s="11" t="inlineStr"/>
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="6" t="inlineStr"/>
       <c r="I31" s="7" t="n"/>
@@ -2420,7 +2429,7 @@
           <t>Клапан муфтовый проходной запорный Ду32Ру10</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr"/>
+      <c r="F34" s="11" t="inlineStr"/>
       <c r="G34" s="5" t="inlineStr"/>
       <c r="H34" s="6" t="inlineStr"/>
       <c r="I34" s="7" t="n"/>
@@ -2532,136 +2541,136 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="n">
+      <c r="A37" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>Штуцерная прочая</t>
         </is>
       </c>
-      <c r="C37" s="11" t="n">
+      <c r="C37" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D37" s="11" t="n"/>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="D37" s="12" t="n"/>
+      <c r="E37" s="13" t="inlineStr">
         <is>
           <t>Клапан для манометра штуцерный сальниковый Ду 6</t>
         </is>
       </c>
-      <c r="F37" s="11" t="inlineStr">
+      <c r="F37" s="12" t="inlineStr">
         <is>
           <t>521-34.3404-03</t>
         </is>
       </c>
-      <c r="G37" s="11" t="inlineStr">
+      <c r="G37" s="12" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="H37" s="12" t="inlineStr"/>
-      <c r="I37" s="13" t="n">
+      <c r="H37" s="13" t="inlineStr"/>
+      <c r="I37" s="14" t="n">
         <v>0.7</v>
       </c>
-      <c r="J37" s="14" t="n">
+      <c r="J37" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="K37" s="14" t="n">
+      <c r="K37" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="L37" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" s="11" t="inlineStr">
+      <c r="L37" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="12" t="inlineStr">
         <is>
           <t>3000 - 4000</t>
         </is>
       </c>
-      <c r="O37" s="11" t="inlineStr">
+      <c r="O37" s="12" t="inlineStr">
         <is>
           <t>14-17000</t>
         </is>
       </c>
-      <c r="P37" s="12" t="inlineStr">
+      <c r="P37" s="13" t="inlineStr">
         <is>
           <t>отгружено 29.09.26</t>
         </is>
       </c>
-      <c r="Q37" s="11" t="inlineStr">
+      <c r="Q37" s="12" t="inlineStr">
         <is>
           <t>Прил. 2</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="n">
+      <c r="A38" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>Штуцерная прочая</t>
         </is>
       </c>
-      <c r="C38" s="11" t="n">
+      <c r="C38" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D38" s="11" t="n">
+      <c r="D38" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E38" s="13" t="inlineStr">
         <is>
           <t>Клапан для манометра штущерный сальниковый Ду6 Ру100 новый                                                                                                       (521-35.3434 -8 шт , 521-02.013 -86 шт , 521-35.3434-04 -30 шт)</t>
         </is>
       </c>
-      <c r="F38" s="11" t="inlineStr">
+      <c r="F38" s="12" t="inlineStr">
         <is>
           <t>521-02.013</t>
         </is>
       </c>
-      <c r="G38" s="11" t="inlineStr">
+      <c r="G38" s="12" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="H38" s="12" t="inlineStr">
+      <c r="H38" s="13" t="inlineStr">
         <is>
           <t>высокое давление Ру100</t>
         </is>
       </c>
-      <c r="I38" s="13" t="n">
+      <c r="I38" s="14" t="n">
         <v>0.7</v>
       </c>
-      <c r="J38" s="14" t="n">
+      <c r="J38" s="15" t="n">
         <v>95</v>
       </c>
-      <c r="K38" s="14" t="n">
+      <c r="K38" s="15" t="n">
         <v>124</v>
       </c>
-      <c r="L38" s="14" t="n">
+      <c r="L38" s="15" t="n">
         <v>29</v>
       </c>
-      <c r="M38" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="11" t="inlineStr">
+      <c r="M38" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="12" t="inlineStr">
         <is>
           <t>3000 - 4000</t>
         </is>
       </c>
-      <c r="O38" s="11" t="inlineStr">
+      <c r="O38" s="12" t="inlineStr">
         <is>
           <t>14-17000</t>
         </is>
       </c>
-      <c r="P38" s="12" t="inlineStr">
+      <c r="P38" s="13" t="inlineStr">
         <is>
           <t>отгружено 29.09.26</t>
         </is>
       </c>
-      <c r="Q38" s="11" t="inlineStr">
+      <c r="Q38" s="12" t="inlineStr">
         <is>
           <t>Прил. 2</t>
         </is>
@@ -3389,7 +3398,7 @@
           <t>Клапан фланц. концевой пожарный угловой Ду50</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr"/>
+      <c r="F51" s="11" t="inlineStr"/>
       <c r="G51" s="5" t="inlineStr">
         <is>
           <t>б/у</t>
@@ -3438,7 +3447,7 @@
           <t>Клапан фланцевый угловой Ду50</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr"/>
+      <c r="F52" s="11" t="inlineStr"/>
       <c r="G52" s="5" t="inlineStr">
         <is>
           <t>б/у</t>
@@ -3833,7 +3842,7 @@
           <t>Клапан фланцевый угловой Ду100</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr"/>
+      <c r="F59" s="11" t="inlineStr"/>
       <c r="G59" s="5" t="inlineStr">
         <is>
           <t>б/у</t>
@@ -3943,7 +3952,7 @@
           <t>Клапан фланцевый угловой Ду150 Ру10</t>
         </is>
       </c>
-      <c r="F61" s="5" t="inlineStr"/>
+      <c r="F61" s="11" t="inlineStr"/>
       <c r="G61" s="5" t="inlineStr"/>
       <c r="H61" s="6" t="inlineStr"/>
       <c r="I61" s="7" t="n"/>
@@ -4013,7 +4022,7 @@
           <t>Клапан фланцевый проходной Ду50</t>
         </is>
       </c>
-      <c r="F63" s="5" t="inlineStr"/>
+      <c r="F63" s="11" t="inlineStr"/>
       <c r="G63" s="5" t="inlineStr">
         <is>
           <t>б/у</t>
@@ -4393,7 +4402,7 @@
           <t>Клапан фланцевый проходной Ду200</t>
         </is>
       </c>
-      <c r="F69" s="5" t="inlineStr"/>
+      <c r="F69" s="11" t="inlineStr"/>
       <c r="G69" s="5" t="inlineStr">
         <is>
           <t>б/у</t>
@@ -4469,7 +4478,7 @@
           <t>Клинкет Ду 200</t>
         </is>
       </c>
-      <c r="F71" s="5" t="inlineStr"/>
+      <c r="F71" s="11" t="inlineStr"/>
       <c r="G71" s="5" t="inlineStr">
         <is>
           <t>б/у</t>
@@ -4526,7 +4535,7 @@
           <t>Клинкет Ду 250</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr"/>
+      <c r="F72" s="11" t="inlineStr"/>
       <c r="G72" s="5" t="inlineStr">
         <is>
           <t>б/у</t>
@@ -4583,7 +4592,7 @@
           <t>Клинкет Ду 300</t>
         </is>
       </c>
-      <c r="F73" s="5" t="inlineStr"/>
+      <c r="F73" s="11" t="inlineStr"/>
       <c r="G73" s="5" t="inlineStr">
         <is>
           <t>б/у</t>
@@ -4640,7 +4649,7 @@
           <t>Клинкет  Ду 350</t>
         </is>
       </c>
-      <c r="F74" s="5" t="inlineStr"/>
+      <c r="F74" s="11" t="inlineStr"/>
       <c r="G74" s="5" t="inlineStr">
         <is>
           <t>б/у</t>
@@ -4720,7 +4729,7 @@
           <t>Фильтр забортной воды Ду 50</t>
         </is>
       </c>
-      <c r="F76" s="5" t="inlineStr"/>
+      <c r="F76" s="11" t="inlineStr"/>
       <c r="G76" s="5" t="inlineStr">
         <is>
           <t>б/у</t>
@@ -4777,7 +4786,7 @@
           <t>Фильтр заборной воды ДУ 80</t>
         </is>
       </c>
-      <c r="F77" s="5" t="inlineStr"/>
+      <c r="F77" s="11" t="inlineStr"/>
       <c r="G77" s="5" t="inlineStr">
         <is>
           <t>б/у</t>
@@ -4826,7 +4835,7 @@
           <t>Фильтр забортной воды Ду 100</t>
         </is>
       </c>
-      <c r="F78" s="5" t="inlineStr"/>
+      <c r="F78" s="11" t="inlineStr"/>
       <c r="G78" s="5" t="inlineStr">
         <is>
           <t>б/у</t>
@@ -4946,7 +4955,7 @@
           <t>Фильтр заборной воды ДУ 150</t>
         </is>
       </c>
-      <c r="F80" s="5" t="inlineStr"/>
+      <c r="F80" s="11" t="inlineStr"/>
       <c r="G80" s="5" t="inlineStr">
         <is>
           <t>б/у</t>
@@ -5003,7 +5012,7 @@
           <t>Фильтр забортной воды Ду200</t>
         </is>
       </c>
-      <c r="F81" s="5" t="inlineStr"/>
+      <c r="F81" s="11" t="inlineStr"/>
       <c r="G81" s="5" t="inlineStr">
         <is>
           <t>б/у</t>
@@ -5043,61 +5052,61 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="11" t="n">
+      <c r="A82" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="B82" s="11" t="inlineStr">
+      <c r="B82" s="12" t="inlineStr">
         <is>
           <t>Фильтры забортной воды</t>
         </is>
       </c>
-      <c r="C82" s="11" t="n">
+      <c r="C82" s="12" t="n">
         <v>300</v>
       </c>
-      <c r="D82" s="11" t="n"/>
-      <c r="E82" s="12" t="inlineStr">
+      <c r="D82" s="12" t="n"/>
+      <c r="E82" s="13" t="inlineStr">
         <is>
           <t>Фильтр забортной воды Ду 300</t>
         </is>
       </c>
-      <c r="F82" s="11" t="inlineStr"/>
-      <c r="G82" s="11" t="inlineStr">
+      <c r="F82" s="12" t="inlineStr"/>
+      <c r="G82" s="12" t="inlineStr">
         <is>
           <t>б/у</t>
         </is>
       </c>
-      <c r="H82" s="12" t="inlineStr"/>
-      <c r="I82" s="13" t="n">
+      <c r="H82" s="13" t="inlineStr"/>
+      <c r="I82" s="14" t="n">
         <v>172</v>
       </c>
-      <c r="J82" s="14" t="n">
+      <c r="J82" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="K82" s="14" t="n">
+      <c r="K82" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="L82" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" s="11" t="inlineStr">
+      <c r="L82" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="12" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="O82" s="11" t="inlineStr">
+      <c r="O82" s="12" t="inlineStr">
         <is>
           <t>800000</t>
         </is>
       </c>
-      <c r="P82" s="12" t="inlineStr">
+      <c r="P82" s="13" t="inlineStr">
         <is>
           <t>отгружено 24.09.26</t>
         </is>
       </c>
-      <c r="Q82" s="11" t="inlineStr">
+      <c r="Q82" s="12" t="inlineStr">
         <is>
           <t>Прил. 2</t>
         </is>
@@ -6412,7 +6421,7 @@
           <t>Коробка 2-х клапановая фланцевая Ду50</t>
         </is>
       </c>
-      <c r="F108" s="5" t="inlineStr"/>
+      <c r="F108" s="11" t="inlineStr"/>
       <c r="G108" s="5" t="inlineStr">
         <is>
           <t>б/у</t>
@@ -6469,7 +6478,7 @@
           <t>Коробка 3-х клап.фланцевая Ду50</t>
         </is>
       </c>
-      <c r="F109" s="5" t="inlineStr"/>
+      <c r="F109" s="11" t="inlineStr"/>
       <c r="G109" s="5" t="inlineStr">
         <is>
           <t>б/у</t>
@@ -6530,7 +6539,7 @@
           <t>Коробка 2-х клапановая фланцевая Ду80</t>
         </is>
       </c>
-      <c r="F110" s="5" t="inlineStr"/>
+      <c r="F110" s="11" t="inlineStr"/>
       <c r="G110" s="5" t="inlineStr">
         <is>
           <t>б/у</t>
@@ -6591,7 +6600,7 @@
           <t>Коробка 3-х клап.фланцевая Ду80</t>
         </is>
       </c>
-      <c r="F111" s="5" t="inlineStr"/>
+      <c r="F111" s="11" t="inlineStr"/>
       <c r="G111" s="5" t="inlineStr">
         <is>
           <t>б/у</t>
@@ -6652,7 +6661,7 @@
           <t>Коробка 3-х клап.фланцевая Ду100</t>
         </is>
       </c>
-      <c r="F112" s="5" t="inlineStr"/>
+      <c r="F112" s="11" t="inlineStr"/>
       <c r="G112" s="5" t="inlineStr">
         <is>
           <t>б/у</t>
@@ -6734,7 +6743,7 @@
           <t>Кран штуцерный спусковой самозапорный проходной Ду15 Ру25</t>
         </is>
       </c>
-      <c r="F114" s="5" t="inlineStr"/>
+      <c r="F114" s="11" t="inlineStr"/>
       <c r="G114" s="5" t="inlineStr"/>
       <c r="H114" s="6" t="inlineStr"/>
       <c r="I114" s="7" t="n">
@@ -6770,67 +6779,67 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="11" t="n">
+      <c r="A115" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="B115" s="11" t="inlineStr">
+      <c r="B115" s="12" t="inlineStr">
         <is>
           <t>Краны</t>
         </is>
       </c>
-      <c r="C115" s="11" t="n">
+      <c r="C115" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="D115" s="11" t="n">
+      <c r="D115" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="E115" s="12" t="inlineStr">
+      <c r="E115" s="13" t="inlineStr">
         <is>
           <t>Кран штуцерный спусковой самозапорный проходной Ду20 Ру10</t>
         </is>
       </c>
-      <c r="F115" s="11" t="inlineStr">
+      <c r="F115" s="12" t="inlineStr">
         <is>
           <t>528-3М129</t>
         </is>
       </c>
-      <c r="G115" s="11" t="inlineStr">
+      <c r="G115" s="12" t="inlineStr">
         <is>
           <t>б/у</t>
         </is>
       </c>
-      <c r="H115" s="12" t="inlineStr"/>
-      <c r="I115" s="13" t="n">
+      <c r="H115" s="13" t="inlineStr"/>
+      <c r="I115" s="14" t="n">
         <v>1.8</v>
       </c>
-      <c r="J115" s="14" t="n">
+      <c r="J115" s="15" t="n">
         <v>36</v>
       </c>
-      <c r="K115" s="14" t="n">
+      <c r="K115" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="L115" s="14" t="n">
+      <c r="L115" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="M115" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N115" s="11" t="inlineStr">
+      <c r="M115" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" s="12" t="inlineStr">
         <is>
           <t>6000</t>
         </is>
       </c>
-      <c r="O115" s="11" t="inlineStr">
+      <c r="O115" s="12" t="inlineStr">
         <is>
           <t>20-22000</t>
         </is>
       </c>
-      <c r="P115" s="12" t="inlineStr">
+      <c r="P115" s="13" t="inlineStr">
         <is>
           <t>отгружено 29.09.26</t>
         </is>
       </c>
-      <c r="Q115" s="11" t="inlineStr">
+      <c r="Q115" s="12" t="inlineStr">
         <is>
           <t>Прил. 2</t>
         </is>
@@ -8036,7 +8045,7 @@
           <t>Клапан фреоновый саленоидный</t>
         </is>
       </c>
-      <c r="F136" s="5" t="inlineStr"/>
+      <c r="F136" s="11" t="inlineStr"/>
       <c r="G136" s="5" t="inlineStr"/>
       <c r="H136" s="9" t="inlineStr">
         <is>
@@ -8081,7 +8090,7 @@
           <t>Эжектор ВЭЖ 6,3</t>
         </is>
       </c>
-      <c r="F137" s="5" t="inlineStr"/>
+      <c r="F137" s="11" t="inlineStr"/>
       <c r="G137" s="5" t="inlineStr">
         <is>
           <t>б/у</t>
@@ -8174,20 +8183,20 @@
       </c>
     </row>
     <row r="139">
-      <c r="E139" s="15" t="inlineStr">
+      <c r="E139" s="16" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="J139" s="16">
+      <c r="J139" s="17">
         <f>SUM(J5:J138)</f>
         <v/>
       </c>
-      <c r="K139" s="16">
+      <c r="K139" s="17">
         <f>SUM(K5:K138)</f>
         <v/>
       </c>
-      <c r="M139" s="16">
+      <c r="M139" s="17">
         <f>SUM(M5:M138)</f>
         <v/>
       </c>
@@ -8268,403 +8277,403 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>Штуцерная угловая</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="18" t="n">
         <v>18</v>
       </c>
-      <c r="C5" s="18" t="n">
+      <c r="C5" s="19" t="n">
         <v>84</v>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="19" t="n">
         <v>78</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="20" t="n">
         <v>-5</v>
       </c>
-      <c r="F5" s="18" t="n">
+      <c r="F5" s="19" t="n">
         <v>216.7</v>
       </c>
-      <c r="G5" s="20" t="n">
+      <c r="G5" s="21" t="n">
         <v>0.01391749300175896</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>Штуцерная проходная</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C6" s="19" t="n">
         <v>816</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="19" t="n">
         <v>812</v>
       </c>
-      <c r="E6" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="18" t="n">
+      <c r="E6" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="19" t="n">
         <v>996.6</v>
       </c>
-      <c r="G6" s="20" t="n">
+      <c r="G6" s="21" t="n">
         <v>0.0640004315501706</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>Штуцерная прочая</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="19" t="n">
         <v>151</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="19" t="n">
         <v>180</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="20" t="n">
         <v>29</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="19" t="n">
         <v>184.3</v>
       </c>
-      <c r="G7" s="20" t="n">
+      <c r="G7" s="21" t="n">
         <v>0.01183873124249844</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>Фланцевая угловая</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B8" s="18" t="n">
         <v>15</v>
       </c>
-      <c r="C8" s="18" t="n">
+      <c r="C8" s="19" t="n">
         <v>56</v>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="19" t="n">
         <v>63</v>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="19" t="n">
         <v>1186.9</v>
       </c>
-      <c r="G8" s="20" t="n">
+      <c r="G8" s="21" t="n">
         <v>0.07622126450621862</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>Фланцевая проходная</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n">
+      <c r="B9" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="18" t="n">
+      <c r="C9" s="19" t="n">
         <v>77</v>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="19" t="n">
         <v>72</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="20" t="n">
         <v>-5</v>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="F9" s="19" t="n">
         <v>1521.2</v>
       </c>
-      <c r="G9" s="20" t="n">
+      <c r="G9" s="21" t="n">
         <v>0.09768960111792045</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>Клинкеты</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B10" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="18" t="n">
+      <c r="C10" s="19" t="n">
         <v>47</v>
       </c>
-      <c r="D10" s="18" t="n">
+      <c r="D10" s="19" t="n">
         <v>48</v>
       </c>
-      <c r="E10" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="18" t="n">
+      <c r="E10" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="19" t="n">
         <v>6419</v>
       </c>
-      <c r="G10" s="20" t="n">
+      <c r="G10" s="21" t="n">
         <v>0.412220319205845</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>Фильтры забортной воды</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n">
+      <c r="B11" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="18" t="n">
+      <c r="C11" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="D11" s="18" t="n">
+      <c r="D11" s="19" t="n">
         <v>21</v>
       </c>
-      <c r="E11" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="18" t="n">
+      <c r="E11" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="19" t="n">
         <v>1656</v>
       </c>
-      <c r="G11" s="20" t="n">
+      <c r="G11" s="21" t="n">
         <v>0.1063462920400186</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>Кингстоны</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n">
+      <c r="B12" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="19" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="G12" s="20" t="n">
+      <c r="G12" s="21" t="n">
         <v>0.006396190028493872</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>Головки вентиляционные</t>
         </is>
       </c>
-      <c r="B13" s="17" t="n">
+      <c r="B13" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="19" t="n">
         <v>43</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="19" t="n">
         <v>43</v>
       </c>
-      <c r="E13" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="18" t="n">
+      <c r="E13" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="19" t="n">
         <v>356.1</v>
       </c>
-      <c r="G13" s="20" t="n">
+      <c r="G13" s="21" t="n">
         <v>0.02286830591512718</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>Колонка смотровая</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n">
+      <c r="B14" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="19" t="n">
         <v>22</v>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="E14" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="18" t="n">
+      <c r="E14" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="G14" s="20" t="n">
+      <c r="G14" s="21" t="n">
         <v>0.0005779689784783618</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>Захлопки</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n">
+      <c r="B15" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="C15" s="18" t="n">
+      <c r="C15" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D15" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="E15" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="18" t="n">
+      <c r="E15" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="19" t="n">
         <v>171</v>
       </c>
-      <c r="G15" s="20" t="n">
+      <c r="G15" s="21" t="n">
         <v>0.01098141059108887</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>Коробки клапанные</t>
         </is>
       </c>
-      <c r="B16" s="17" t="n">
+      <c r="B16" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="C16" s="18" t="n">
+      <c r="C16" s="19" t="n">
         <v>27</v>
       </c>
-      <c r="D16" s="18" t="n">
+      <c r="D16" s="19" t="n">
         <v>35</v>
       </c>
-      <c r="E16" s="19" t="n">
+      <c r="E16" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="F16" s="18" t="n">
+      <c r="F16" s="19" t="n">
         <v>1885.5</v>
       </c>
-      <c r="G16" s="20" t="n">
+      <c r="G16" s="21" t="n">
         <v>0.1210845009912168</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>Краны</t>
         </is>
       </c>
-      <c r="B17" s="17" t="n">
+      <c r="B17" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="C17" s="18" t="n">
+      <c r="C17" s="19" t="n">
         <v>53</v>
       </c>
-      <c r="D17" s="18" t="n">
+      <c r="D17" s="19" t="n">
         <v>57</v>
       </c>
-      <c r="E17" s="19" t="n">
+      <c r="E17" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="F17" s="18" t="n">
+      <c r="F17" s="19" t="n">
         <v>44.1</v>
       </c>
-      <c r="G17" s="20" t="n">
+      <c r="G17" s="21" t="n">
         <v>0.002832047994543973</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>Стаканы переборочные</t>
         </is>
       </c>
-      <c r="B18" s="17" t="n">
+      <c r="B18" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="C18" s="18" t="n">
+      <c r="C18" s="19" t="n">
         <v>18</v>
       </c>
-      <c r="D18" s="18" t="n">
+      <c r="D18" s="19" t="n">
         <v>36</v>
       </c>
-      <c r="E18" s="19" t="n">
+      <c r="E18" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="F18" s="18" t="n">
+      <c r="F18" s="19" t="n">
         <v>52.1</v>
       </c>
-      <c r="G18" s="20" t="n">
+      <c r="G18" s="21" t="n">
         <v>0.00334579819763585</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>Прочее</t>
         </is>
       </c>
-      <c r="B19" s="17" t="n">
+      <c r="B19" s="18" t="n">
         <v>12</v>
       </c>
-      <c r="C19" s="18" t="n">
+      <c r="C19" s="19" t="n">
         <v>97</v>
       </c>
-      <c r="D19" s="18" t="n">
+      <c r="D19" s="19" t="n">
         <v>95</v>
       </c>
-      <c r="E19" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="18" t="n">
+      <c r="E19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="19" t="n">
         <v>773.6</v>
       </c>
-      <c r="G19" s="20" t="n">
+      <c r="G19" s="21" t="n">
         <v>0.04967964463898453</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="17">
         <f>SUM(B5:B19)</f>
         <v/>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="17">
         <f>SUM(C5:C19)</f>
         <v/>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="17">
         <f>SUM(D5:D19)</f>
         <v/>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="17">
         <f>SUM(E5:E19)</f>
         <v/>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="17">
         <f>SUM(F5:F19)</f>
         <v/>
       </c>
@@ -8680,7 +8689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -8688,13 +8697,14 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="52" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8707,7 +8717,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Высоким давлением считаем Ру от 100. Котельная — паровой клапан, сигнальные предохранительные и водоуказательная колонка. Эти позиции стоят дороже обычных и спрашивают их отдельно.</t>
+          <t>Высоким давлением считаем Ру от 100. Котельная — паровой клапан, сигнальные предохранительные и водоуказательная колонка. Оранжевым в колонке «Кол-во факт» — то, что менеджер не пересчитала.</t>
         </is>
       </c>
     </row>
@@ -8739,7 +8749,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Обозначение</t>
+          <t>Чертеж</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -8749,25 +8759,30 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
+          <t>Кол-во по приложению</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>Кол-во факт</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Вес 1 шт, кг</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Общий вес, кг</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Цена по договору</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Ориентир реализации</t>
         </is>
@@ -8790,6 +8805,7 @@
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -8823,21 +8839,24 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="I6" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="J6" s="7" t="n">
+      <c r="K6" s="7" t="n">
         <v>17.5</v>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>25-35000</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="M6" s="5" t="inlineStr">
         <is>
           <t>80-100000</t>
         </is>
@@ -8875,21 +8894,24 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="7" t="n">
-        <v>9.699999999999999</v>
+      <c r="H7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="J7" s="7" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K7" s="7" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>40-55000</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>120-140000</t>
         </is>
@@ -8912,6 +8934,7 @@
       <c r="J8" s="4" t="n"/>
       <c r="K8" s="4" t="n"/>
       <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -8945,21 +8968,24 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H9" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I9" s="7" t="n">
+      <c r="I9" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" s="7" t="n">
         <v>1.1</v>
       </c>
-      <c r="J9" s="7" t="n">
+      <c r="K9" s="7" t="n">
         <v>2.2</v>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -8993,21 +9019,24 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="H10" s="8" t="n">
+        <v>95</v>
+      </c>
+      <c r="I10" s="8" t="n">
         <v>124</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="J10" s="7" t="n">
         <v>0.7</v>
       </c>
-      <c r="J10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="K10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
         <is>
           <t>3000 - 4000</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr">
+      <c r="M10" s="5" t="inlineStr">
         <is>
           <t>14-17000</t>
         </is>
@@ -9045,21 +9074,24 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="7" t="n">
-        <v>3.5</v>
+      <c r="H11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="J11" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="K11" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>20000</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>55000</t>
         </is>
@@ -9097,21 +9129,24 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="H12" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I12" s="7" t="n">
+      <c r="I12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" s="7" t="n">
         <v>2.06</v>
       </c>
-      <c r="J12" s="7" t="n">
+      <c r="K12" s="7" t="n">
         <v>4.12</v>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="L12" s="5" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -9145,21 +9180,24 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="H13" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="I13" s="7" t="n">
+      <c r="I13" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" s="7" t="n">
         <v>0.6</v>
       </c>
-      <c r="J13" s="7" t="n">
+      <c r="K13" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -9193,21 +9231,24 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H14" s="5" t="n">
+      <c r="H14" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="I14" s="7" t="n">
+      <c r="I14" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" s="7" t="n">
         <v>0.7</v>
       </c>
-      <c r="J14" s="7" t="n">
+      <c r="K14" s="7" t="n">
         <v>4.2</v>
       </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="L14" s="5" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr">
+      <c r="M14" s="5" t="inlineStr">
         <is>
           <t>15000</t>
         </is>
@@ -9245,21 +9286,24 @@
           <t>б/у?</t>
         </is>
       </c>
-      <c r="H15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="7" t="n">
-        <v>7.5</v>
+      <c r="H15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="J15" s="7" t="n">
         <v>7.5</v>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="K15" s="7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
         <is>
           <t>15000</t>
         </is>
       </c>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="M15" s="5" t="inlineStr">
         <is>
           <t>45000</t>
         </is>
@@ -9297,21 +9341,24 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H16" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="7" t="n">
-        <v>7.5</v>
+      <c r="H16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="J16" s="7" t="n">
         <v>7.5</v>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="K16" s="7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
         <is>
           <t>15000</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="M16" s="5" t="inlineStr">
         <is>
           <t>45000</t>
         </is>
@@ -9349,21 +9396,24 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="7" t="n">
-        <v>3.8</v>
+      <c r="H17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="J17" s="7" t="n">
         <v>3.8</v>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="K17" s="7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>20000</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="M17" s="5" t="inlineStr">
         <is>
           <t>65000</t>
         </is>
@@ -9397,19 +9447,22 @@
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="7" t="n">
+      <c r="H18" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="10" t="n"/>
+      <c r="J18" s="7" t="n">
         <v>3.64</v>
       </c>
-      <c r="J18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="K18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -9443,21 +9496,24 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H19" s="5" t="n">
+      <c r="H19" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="I19" s="7" t="n">
+      <c r="I19" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" s="7" t="n">
         <v>4.3</v>
       </c>
-      <c r="J19" s="7" t="n">
+      <c r="K19" s="7" t="n">
         <v>17.2</v>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -9491,21 +9547,24 @@
           <t>б/у</t>
         </is>
       </c>
-      <c r="H20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="7" t="n">
+      <c r="H20" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="7" t="n">
         <v>1.9</v>
       </c>
-      <c r="J20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="K20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
         <is>
           <t>4000</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="M20" s="5" t="inlineStr">
         <is>
           <t>18000</t>
         </is>
@@ -9543,21 +9602,24 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H21" s="5" t="n">
+      <c r="H21" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I21" s="7" t="n">
+      <c r="I21" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" s="7" t="n">
         <v>1.7</v>
       </c>
-      <c r="J21" s="7" t="n">
+      <c r="K21" s="7" t="n">
         <v>5.1</v>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -9591,21 +9653,24 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H22" s="5" t="n">
+      <c r="H22" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I22" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="I22" s="7" t="n">
+      <c r="J22" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="J22" s="7" t="n">
+      <c r="K22" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="L22" s="5" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -9639,21 +9704,24 @@
           <t>б/у</t>
         </is>
       </c>
-      <c r="H23" s="5" t="n">
+      <c r="H23" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="I23" s="7" t="n">
+      <c r="I23" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="J23" s="7" t="n">
         <v>5.6</v>
       </c>
-      <c r="J23" s="7" t="n">
+      <c r="K23" s="7" t="n">
         <v>39.2</v>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>25000</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="M23" s="5" t="inlineStr">
         <is>
           <t>45000-65000</t>
         </is>
@@ -9691,21 +9759,24 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H24" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" s="7" t="n">
-        <v>2.3</v>
+      <c r="H24" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="J24" s="7" t="n">
         <v>2.3</v>
       </c>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="K24" s="7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -9739,21 +9810,24 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="7" t="n">
-        <v>1.8</v>
+      <c r="H25" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="J25" s="7" t="n">
         <v>1.8</v>
       </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="K25" s="7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>4500</t>
         </is>
       </c>
-      <c r="L25" s="5" t="inlineStr">
+      <c r="M25" s="5" t="inlineStr">
         <is>
           <t>22000</t>
         </is>
@@ -9791,21 +9865,24 @@
           <t>новый ?</t>
         </is>
       </c>
-      <c r="H26" s="5" t="n">
+      <c r="H26" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="I26" s="7" t="n">
+      <c r="I26" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J26" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="J26" s="7" t="n">
+      <c r="K26" s="7" t="n">
         <v>243</v>
       </c>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="L26" s="5" t="inlineStr">
         <is>
           <t>35000</t>
         </is>
       </c>
-      <c r="L26" s="5" t="inlineStr">
+      <c r="M26" s="5" t="inlineStr">
         <is>
           <t>90-120000</t>
         </is>
@@ -9843,21 +9920,24 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" s="7" t="n">
-        <v>2.9</v>
+      <c r="H27" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="J27" s="7" t="n">
         <v>2.9</v>
       </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="K27" s="7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>5000</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr">
+      <c r="M27" s="5" t="inlineStr">
         <is>
           <t>20000</t>
         </is>
@@ -9895,21 +9975,24 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H28" s="5" t="n">
+      <c r="H28" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I28" s="7" t="n">
+      <c r="I28" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" s="7" t="n">
         <v>2.5</v>
       </c>
-      <c r="J28" s="7" t="n">
+      <c r="K28" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="L28" s="5" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -9943,21 +10026,24 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H29" s="5" t="n">
+      <c r="H29" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="I29" s="7" t="n">
+      <c r="I29" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="J29" s="7" t="n">
         <v>3.3</v>
       </c>
-      <c r="J29" s="7" t="n">
+      <c r="K29" s="7" t="n">
         <v>102.3</v>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="L29" s="5" t="inlineStr">
         <is>
           <t>6500</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="M29" s="5" t="inlineStr">
         <is>
           <t>22000</t>
         </is>
@@ -9995,21 +10081,24 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H30" s="5" t="n">
+      <c r="H30" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="I30" s="7" t="n">
+      <c r="I30" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="J30" s="7" t="n">
         <v>3.3</v>
       </c>
-      <c r="J30" s="7" t="n">
+      <c r="K30" s="7" t="n">
         <v>46.2</v>
       </c>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="L30" s="5" t="inlineStr">
         <is>
           <t>6500</t>
         </is>
       </c>
-      <c r="L30" s="5" t="inlineStr">
+      <c r="M30" s="5" t="inlineStr">
         <is>
           <t>22000</t>
         </is>
@@ -10047,21 +10136,24 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" s="7" t="n">
-        <v>3.3</v>
+      <c r="H31" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="J31" s="7" t="n">
         <v>3.3</v>
       </c>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="K31" s="7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
         <is>
           <t>6500</t>
         </is>
       </c>
-      <c r="L31" s="5" t="inlineStr">
+      <c r="M31" s="5" t="inlineStr">
         <is>
           <t>22000</t>
         </is>
@@ -10099,21 +10191,24 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H32" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" s="7" t="n">
-        <v>3.3</v>
+      <c r="H32" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="J32" s="7" t="n">
         <v>3.3</v>
       </c>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="K32" s="7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
         <is>
           <t>6500</t>
         </is>
       </c>
-      <c r="L32" s="5" t="inlineStr">
+      <c r="M32" s="5" t="inlineStr">
         <is>
           <t>22000</t>
         </is>
@@ -10151,21 +10246,24 @@
           <t>б/у</t>
         </is>
       </c>
-      <c r="H33" s="5" t="n">
+      <c r="H33" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="I33" s="7" t="n">
+      <c r="I33" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="J33" s="7" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="J33" s="7" t="n">
+      <c r="K33" s="7" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="L33" s="5" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
-      <c r="L33" s="5" t="inlineStr">
+      <c r="M33" s="5" t="inlineStr">
         <is>
           <t>50000-70000</t>
         </is>
@@ -10201,21 +10299,24 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H34" s="5" t="n">
+      <c r="H34" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="I34" s="7" t="n">
-        <v>1</v>
+      <c r="I34" s="8" t="n">
+        <v>8</v>
       </c>
       <c r="J34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="L34" s="5" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="L34" s="5" t="inlineStr">
+      <c r="M34" s="5" t="inlineStr">
         <is>
           <t>12000</t>
         </is>
@@ -10238,6 +10339,7 @@
       <c r="J35" s="4" t="n"/>
       <c r="K35" s="4" t="n"/>
       <c r="L35" s="4" t="n"/>
+      <c r="M35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -10271,21 +10373,24 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H36" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" s="7" t="n">
-        <v>3.5</v>
+      <c r="H36" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="J36" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="K36" s="5" t="inlineStr">
+      <c r="K36" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
         <is>
           <t>20000</t>
         </is>
       </c>
-      <c r="L36" s="5" t="inlineStr">
+      <c r="M36" s="5" t="inlineStr">
         <is>
           <t>55000</t>
         </is>
@@ -10323,21 +10428,24 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H37" s="5" t="n">
+      <c r="H37" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I37" s="7" t="n">
+      <c r="I37" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J37" s="7" t="n">
         <v>2.06</v>
       </c>
-      <c r="J37" s="7" t="n">
+      <c r="K37" s="7" t="n">
         <v>4.12</v>
       </c>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="L37" s="5" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="L37" s="5" t="inlineStr"/>
+      <c r="M37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -10371,21 +10479,24 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H38" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" s="7" t="n">
-        <v>0.77</v>
+      <c r="H38" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="J38" s="7" t="n">
         <v>0.77</v>
       </c>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="K38" s="7" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
         <is>
           <t>3500</t>
         </is>
       </c>
-      <c r="L38" s="5" t="inlineStr">
+      <c r="M38" s="5" t="inlineStr">
         <is>
           <t>15000</t>
         </is>
@@ -10423,21 +10534,24 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I39" s="7" t="n">
-        <v>1.24</v>
+      <c r="H39" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="J39" s="7" t="n">
         <v>1.24</v>
       </c>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="K39" s="7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>3500</t>
         </is>
       </c>
-      <c r="L39" s="5" t="inlineStr">
+      <c r="M39" s="5" t="inlineStr">
         <is>
           <t>15000</t>
         </is>
@@ -10471,17 +10585,20 @@
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr"/>
-      <c r="H40" s="5" t="n"/>
-      <c r="I40" s="7" t="n"/>
-      <c r="J40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="5" t="inlineStr">
+      <c r="H40" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="I40" s="10" t="n"/>
+      <c r="J40" s="7" t="n"/>
+      <c r="K40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
         <is>
           <t>12000</t>
         </is>
       </c>
-      <c r="L40" s="5" t="inlineStr">
+      <c r="M40" s="5" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
@@ -10519,21 +10636,24 @@
           <t>б/у</t>
         </is>
       </c>
-      <c r="H41" s="5" t="n">
+      <c r="H41" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="I41" s="7" t="n">
+      <c r="I41" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J41" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="J41" s="7" t="n">
+      <c r="K41" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="K41" s="5" t="inlineStr">
+      <c r="L41" s="5" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="L41" s="5" t="inlineStr"/>
+      <c r="M41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -10567,21 +10687,24 @@
           <t>новый?</t>
         </is>
       </c>
-      <c r="H42" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" s="7" t="n">
-        <v>32.6</v>
+      <c r="H42" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="J42" s="7" t="n">
         <v>32.6</v>
       </c>
-      <c r="K42" s="5" t="inlineStr">
+      <c r="K42" s="7" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
         <is>
           <t>50-60</t>
         </is>
       </c>
-      <c r="L42" s="5" t="inlineStr">
+      <c r="M42" s="5" t="inlineStr">
         <is>
           <t>120-160000</t>
         </is>
@@ -10604,6 +10727,7 @@
       <c r="J43" s="4" t="n"/>
       <c r="K43" s="4" t="n"/>
       <c r="L43" s="4" t="n"/>
+      <c r="M43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -10635,21 +10759,24 @@
           <t>б/у</t>
         </is>
       </c>
-      <c r="H44" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" s="7" t="n">
-        <v>5.5</v>
+      <c r="H44" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="J44" s="7" t="n">
         <v>5.5</v>
       </c>
-      <c r="K44" s="5" t="inlineStr">
+      <c r="K44" s="7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
         <is>
           <t>15000</t>
         </is>
       </c>
-      <c r="L44" s="5" t="inlineStr">
+      <c r="M44" s="5" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
@@ -10685,21 +10812,24 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H45" s="5" t="n">
+      <c r="H45" s="8" t="n">
         <v>62</v>
       </c>
-      <c r="I45" s="7" t="n">
+      <c r="I45" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="J45" s="7" t="n">
         <v>5.5</v>
       </c>
-      <c r="J45" s="7" t="n">
+      <c r="K45" s="7" t="n">
         <v>341</v>
       </c>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="L45" s="5" t="inlineStr">
         <is>
           <t>15000</t>
         </is>
       </c>
-      <c r="L45" s="5" t="inlineStr">
+      <c r="M45" s="5" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
@@ -10722,6 +10852,7 @@
       <c r="J46" s="4" t="n"/>
       <c r="K46" s="4" t="n"/>
       <c r="L46" s="4" t="n"/>
+      <c r="M46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -10753,21 +10884,24 @@
           <t>новый ?</t>
         </is>
       </c>
-      <c r="H47" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I47" s="7" t="n">
-        <v>11.6</v>
+      <c r="H47" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="J47" s="7" t="n">
         <v>11.6</v>
       </c>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="K47" s="7" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
         <is>
           <t>25000</t>
         </is>
       </c>
-      <c r="L47" s="5" t="inlineStr">
+      <c r="M47" s="5" t="inlineStr">
         <is>
           <t>55000</t>
         </is>
@@ -10801,21 +10935,24 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H48" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I48" s="7" t="n">
-        <v>12.3</v>
+      <c r="H48" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="J48" s="7" t="n">
         <v>12.3</v>
       </c>
-      <c r="K48" s="5" t="inlineStr">
+      <c r="K48" s="7" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="L48" s="5" t="inlineStr"/>
+      <c r="M48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -10835,19 +10972,22 @@
           <t>Клапан фреоновый саленоидный</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr"/>
+      <c r="F49" s="11" t="inlineStr"/>
       <c r="G49" s="5" t="inlineStr"/>
-      <c r="H49" s="5" t="n"/>
-      <c r="I49" s="7" t="n"/>
-      <c r="J49" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="5" t="inlineStr">
+      <c r="H49" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I49" s="10" t="n"/>
+      <c r="J49" s="7" t="n"/>
+      <c r="K49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="L49" s="5" t="inlineStr"/>
+      <c r="M49" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10855,6 +10995,1004 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Позиции без чертежа — вписать</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Покупатель ищет по номеру чертежа. Желтые ячейки заполняем сами: чертеж обычно выбит на корпусе или на бирке.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Группа</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Ду</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Ру</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Чертеж — вписать</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Состояние</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Кол-во факт</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Вес 1 шт, кг</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Лист</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Клапан муфтовый проходной запорный Ду20Ру16</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="n"/>
+      <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="7" t="n"/>
+      <c r="I5" s="7" t="n"/>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Прил. 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Клапан муфтовый проходной запорный Ду32Ру10</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="n"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Прил. 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Фланцевая угловая</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Клапан фланц. концевой пожарный угловой Ду50</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>б/у</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Прил. 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Фланцевая угловая</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый угловой Ду50</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>б/у</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Прил. 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Фланцевая угловая</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый угловой Ду100</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="n"/>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>б/у</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Прил. 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Фланцевая угловая</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый угловой Ду150 Ру10</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="n"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Прил. 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Фланцевая проходная</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый проходной Ду50</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="n"/>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>б/у</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Прил. 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Фланцевая проходная</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый проходной Ду200</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>б/у</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>110</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Прил. 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Клинкеты</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Клинкет Ду 200</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="n"/>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>б/у</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>88</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Прил. 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Клинкеты</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Клинкет Ду 250</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="n"/>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>б/у</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>125</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Прил. 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Клинкеты</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Клинкет Ду 300</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="n"/>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>б/у</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>192</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Прил. 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Клинкеты</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Клинкет  Ду 350</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="n"/>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>б/у</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>228</v>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Прил. 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Фильтры забортной воды</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Фильтр забортной воды Ду 50</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="n"/>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>б/у</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Прил. 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Фильтры забортной воды</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Фильтр заборной воды ДУ 80</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>б/у</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Прил. 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Фильтры забортной воды</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Фильтр забортной воды Ду 100</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="n"/>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>б/у</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Прил. 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Фильтры забортной воды</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Фильтр заборной воды ДУ 150</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="n"/>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>б/у</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Прил. 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Фильтры забортной воды</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Фильтр забортной воды Ду200</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="n"/>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>б/у</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>148</v>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Прил. 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Фильтры забортной воды</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Фильтр забортной воды Ду 300</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="n"/>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>б/у</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>172</v>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Прил. 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Коробки клапанные</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Коробка 2-х клапановая фланцевая Ду50</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="n"/>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>б/у</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Прил. 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Коробки клапанные</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Коробка 3-х клап.фланцевая Ду50</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="n"/>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>б/у</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Прил. 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Коробки клапанные</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Коробка 2-х клапановая фланцевая Ду80</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="n"/>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>б/у</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Прил. 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Коробки клапанные</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Коробка 3-х клап.фланцевая Ду80</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="n"/>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>б/у</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>68</v>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Прил. 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Коробки клапанные</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>Коробка 3-х клап.фланцевая Ду100</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="n"/>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>б/у</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Прил. 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Краны</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>Кран штуцерный спусковой самозапорный проходной Ду15 Ру25</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="n"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>Прил. 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Клапан фреоновый саленоидный</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="n"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="7" t="n"/>
+      <c r="I29" s="7" t="n"/>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Прил. 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Эжектор ВЭЖ 6,3</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="n"/>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>б/у</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>Прил. 3</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10907,7 +12045,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Обозначение</t>
+          <t>Чертеж</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -10942,7 +12080,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>состояние под вопросом</t>
         </is>
@@ -10980,7 +12118,7 @@
       <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>состояние под вопросом</t>
         </is>
@@ -11018,7 +12156,7 @@
       <c r="J6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="22" t="inlineStr">
         <is>
           <t>состояние под вопросом</t>
         </is>
@@ -11056,7 +12194,7 @@
       <c r="J7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>состояние под вопросом</t>
         </is>
@@ -11094,7 +12232,7 @@
       <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением</t>
         </is>
@@ -11132,7 +12270,7 @@
       <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением</t>
         </is>
@@ -11170,7 +12308,7 @@
       <c r="J10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением</t>
         </is>
@@ -11208,7 +12346,7 @@
       <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением</t>
         </is>
@@ -11242,7 +12380,7 @@
       <c r="J12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением</t>
         </is>
@@ -11276,7 +12414,7 @@
       <c r="J13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением; перепроверить</t>
         </is>
@@ -11314,7 +12452,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением; перепроверить</t>
         </is>
@@ -11352,7 +12490,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="21" t="inlineStr">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением; перепроверить</t>
         </is>
@@ -11390,7 +12528,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="inlineStr">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением</t>
         </is>
@@ -11424,7 +12562,7 @@
       <c r="J17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="21" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением; уже отгружено; общий вес не посчитан</t>
         </is>
@@ -11466,7 +12604,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="inlineStr">
+      <c r="A19" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением</t>
         </is>
@@ -11504,7 +12642,7 @@
       <c r="J19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="inlineStr">
+      <c r="A20" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением</t>
         </is>
@@ -11542,7 +12680,7 @@
       <c r="J20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>состояние под вопросом</t>
         </is>
@@ -11580,7 +12718,7 @@
       <c r="J21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="21" t="inlineStr">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>еще раз посчитать; состояние под вопросом</t>
         </is>
@@ -11622,7 +12760,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>состояние под вопросом</t>
         </is>
@@ -11660,7 +12798,7 @@
       <c r="J23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением</t>
         </is>
@@ -11698,7 +12836,7 @@
       <c r="J24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="A25" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением</t>
         </is>
@@ -11732,7 +12870,7 @@
       <c r="J25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="21" t="inlineStr">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением</t>
         </is>
@@ -11766,7 +12904,7 @@
       <c r="J26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="inlineStr">
+      <c r="A27" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением</t>
         </is>
@@ -11804,7 +12942,7 @@
       <c r="J27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="21" t="inlineStr">
+      <c r="A28" s="22" t="inlineStr">
         <is>
           <t>уже отгружено; общий вес не посчитан</t>
         </is>
@@ -11842,7 +12980,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="21" t="inlineStr">
+      <c r="A29" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением</t>
         </is>
@@ -11876,7 +13014,7 @@
       <c r="J29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="21" t="inlineStr">
+      <c r="A30" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением</t>
         </is>
@@ -11914,7 +13052,7 @@
       <c r="J30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="21" t="inlineStr">
+      <c r="A31" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением</t>
         </is>
@@ -11952,7 +13090,7 @@
       <c r="J31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="21" t="inlineStr">
+      <c r="A32" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением</t>
         </is>
@@ -11990,7 +13128,7 @@
       <c r="J32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="21" t="inlineStr">
+      <c r="A33" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением</t>
         </is>
@@ -12028,7 +13166,7 @@
       <c r="J33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="21" t="inlineStr">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением</t>
         </is>
@@ -12062,7 +13200,7 @@
       <c r="J34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="21" t="inlineStr">
+      <c r="A35" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением</t>
         </is>
@@ -12100,7 +13238,7 @@
       <c r="J35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="21" t="inlineStr">
+      <c r="A36" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением</t>
         </is>
@@ -12138,7 +13276,7 @@
       <c r="J36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="21" t="inlineStr">
+      <c r="A37" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением</t>
         </is>
@@ -12176,7 +13314,7 @@
       <c r="J37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="21" t="inlineStr">
+      <c r="A38" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением</t>
         </is>
@@ -12214,7 +13352,7 @@
       <c r="J38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="21" t="inlineStr">
+      <c r="A39" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением</t>
         </is>
@@ -12252,7 +13390,7 @@
       <c r="J39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="21" t="inlineStr">
+      <c r="A40" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением</t>
         </is>
@@ -12286,7 +13424,7 @@
       <c r="J40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="21" t="inlineStr">
+      <c r="A41" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением</t>
         </is>
@@ -12324,7 +13462,7 @@
       <c r="J41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="21" t="inlineStr">
+      <c r="A42" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением</t>
         </is>
@@ -12356,7 +13494,7 @@
       <c r="J42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="21" t="inlineStr">
+      <c r="A43" s="22" t="inlineStr">
         <is>
           <t>перепроверить кол-во</t>
         </is>
@@ -12398,7 +13536,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="21" t="inlineStr">
+      <c r="A44" s="22" t="inlineStr">
         <is>
           <t>не нашла  еще</t>
         </is>
@@ -12436,7 +13574,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="21" t="inlineStr">
+      <c r="A45" s="22" t="inlineStr">
         <is>
           <t>уже отгружено; общий вес не посчитан</t>
         </is>
@@ -12478,7 +13616,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="21" t="inlineStr">
+      <c r="A46" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением; уже отгружено; общий вес не посчитан</t>
         </is>
@@ -12520,7 +13658,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="21" t="inlineStr">
+      <c r="A47" s="22" t="inlineStr">
         <is>
           <t>состояние под вопросом</t>
         </is>
@@ -12558,7 +13696,7 @@
       <c r="J47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="21" t="inlineStr">
+      <c r="A48" s="22" t="inlineStr">
         <is>
           <t>факт не сходится с приложением</t>
         </is>

--- a/outputs/marine_equipment/Остатки_Питер_по_группам.xlsx
+++ b/outputs/marine_equipment/Остатки_Питер_по_группам.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="По группам" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Сводка по группам" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Выделенные позиции" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Ценные группы" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Без чертежа" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Расхождения и вопросы" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -782,7 +782,7 @@
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>высокое давление Ру160</t>
+          <t>воздух высокого давления Ру160</t>
         </is>
       </c>
       <c r="I7" s="7" t="n">
@@ -849,7 +849,7 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>высокое давление Ру200</t>
+          <t>воздух высокого давления Ру200</t>
         </is>
       </c>
       <c r="I8" s="7" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>высокое давление Ру200</t>
+          <t>воздух высокого давления Ру200</t>
         </is>
       </c>
       <c r="I9" s="7" t="n">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>высокое давление Ру160</t>
+          <t>воздух высокого давления Ру160</t>
         </is>
       </c>
       <c r="I12" s="7" t="n">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>высокое давление Ру160</t>
+          <t>воздух высокого давления Ру160</t>
         </is>
       </c>
       <c r="I15" s="7" t="n">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>высокое давление Ру400</t>
+          <t>воздух высокого давления Ру400</t>
         </is>
       </c>
       <c r="I27" s="7" t="n">
@@ -2087,7 +2087,7 @@
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>высокое давление Ру400</t>
+          <t>воздух высокого давления Ру400</t>
         </is>
       </c>
       <c r="I28" s="7" t="n">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>высокое давление Ру160</t>
+          <t>воздух высокого давления Ру160</t>
         </is>
       </c>
       <c r="I32" s="7" t="n">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
-          <t>высокое давление Ру400</t>
+          <t>воздух высокого давления Ру400</t>
         </is>
       </c>
       <c r="I36" s="7" t="n">
@@ -7201,11 +7201,7 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H122" s="9" t="inlineStr">
-        <is>
-          <t>высокое давление Ру100</t>
-        </is>
-      </c>
+      <c r="H122" s="6" t="inlineStr"/>
       <c r="I122" s="7" t="n">
         <v>0.6</v>
       </c>
@@ -7264,11 +7260,7 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H123" s="9" t="inlineStr">
-        <is>
-          <t>высокое давление Ру100</t>
-        </is>
-      </c>
+      <c r="H123" s="6" t="inlineStr"/>
       <c r="I123" s="7" t="n">
         <v>1.7</v>
       </c>
@@ -7327,11 +7319,7 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H124" s="9" t="inlineStr">
-        <is>
-          <t>высокое давление Ру100</t>
-        </is>
-      </c>
+      <c r="H124" s="6" t="inlineStr"/>
       <c r="I124" s="7" t="n">
         <v>1.5</v>
       </c>
@@ -7390,11 +7378,7 @@
           <t>новый</t>
         </is>
       </c>
-      <c r="H125" s="9" t="inlineStr">
-        <is>
-          <t>высокое давление Ру100</t>
-        </is>
-      </c>
+      <c r="H125" s="6" t="inlineStr"/>
       <c r="I125" s="7" t="n">
         <v>2.5</v>
       </c>
@@ -7600,7 +7584,7 @@
       </c>
       <c r="H129" s="9" t="inlineStr">
         <is>
-          <t>высокое давление Ру125</t>
+          <t>воздух высокого давления Ру125</t>
         </is>
       </c>
       <c r="I129" s="7" t="n">
@@ -7667,7 +7651,7 @@
       </c>
       <c r="H130" s="9" t="inlineStr">
         <is>
-          <t>высокое давление Ру400</t>
+          <t>воздух высокого давления Ру400</t>
         </is>
       </c>
       <c r="I130" s="7" t="n">
@@ -7868,7 +7852,7 @@
       </c>
       <c r="H133" s="9" t="inlineStr">
         <is>
-          <t>высокое давление Ру125</t>
+          <t>воздух высокого давления Ру125</t>
         </is>
       </c>
       <c r="I133" s="7" t="n">
@@ -8689,7 +8673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -8710,14 +8694,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Титан, высокое давление, котельная арматура, педальные и электромагнитные</t>
+          <t>Ценные группы: что продается дороже обычной арматуры</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Высоким давлением считаем Ру от 100. Котельная — паровой клапан, сигнальные предохранительные и водоуказательная колонка. Оранжевым в колонке «Кол-во факт» — то, что менеджер не пересчитала.</t>
+          <t>Титан, электромагнитные, котельная, воздух высокого давления и прочая арматура высокого давления. Воздушной ВД считаем пусковые клапаны и все, что от Ру160 — это баллоны и магистрали ВВД. Ру 100-150 — отдельная группа. Оранжевым в колонке «Кол-во факт» — то, что менеджер не пересчитала. Позиция может попасть в два блока: сигнальный предохранительный клапан это и котельная арматура, и высокое давление.</t>
         </is>
       </c>
     </row>
@@ -8791,7 +8775,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Титан — 2 позиций, 6 шт</t>
+          <t>Титановая арматура — 2 позиций  6 шт по приложению  6 шт по факту  27 кг</t>
         </is>
       </c>
       <c r="B5" s="4" t="n"/>
@@ -8920,7 +8904,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Высокое давление — 26 позиций, 260 шт</t>
+          <t>Электромагнитные клапаны — 3 позиций  4 шт по приложению  2 шт по факту  24 кг</t>
         </is>
       </c>
       <c r="B8" s="4" t="n"/>
@@ -8939,79 +8923,77 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>высокое давление Ру400</t>
+          <t>электромагнитный</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Штуцерная прочая</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>400</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="D9" s="5" t="n"/>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Клапан для манометра штущерный  Ду3Ру400 новый</t>
+          <t>Клапан с электромагнитным ручным управлением Ду20/10 перем. 220В</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>521-03.406</t>
+          <t>587-35.8490-04</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>новый</t>
+          <t>новый ?</t>
         </is>
       </c>
       <c r="H9" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>1.1</v>
+        <v>11.6</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>2.2</v>
+        <v>11.6</v>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr"/>
+          <t>25000</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>55000</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>высокое давление Ру100</t>
+          <t>электромагнитный</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Штуцерная прочая</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>100</v>
-      </c>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Клапан для манометра штущерный сальниковый Ду6 Ру100 новый                                                                                                       (521-35.3434 -8 шт , 521-02.013 -86 шт , 521-35.3434-04 -30 шт)</t>
+          <t>Клапан с электромагнитным ручным управлением</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>521-02.013</t>
+          <t>587-182.126</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -9020,159 +9002,103 @@
         </is>
       </c>
       <c r="H10" s="8" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>124</v>
+        <v>1</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>0.7</v>
+        <v>12.3</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>0</v>
+        <v>12.3</v>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>3000 - 4000</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>14-17000</t>
-        </is>
-      </c>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>высокое давление Ру100; котельная</t>
+          <t>электромагнитный</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Штуцерная прочая</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>100</v>
-      </c>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Клапан предохранительный штуцерный сигнальный Ду6 Ру100-230</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>524-35.2423-01</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>новый</t>
-        </is>
-      </c>
+          <t>Клапан фреоновый саленоидный</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
       <c r="H11" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="7" t="n">
-        <v>3.5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="I11" s="10" t="n"/>
+      <c r="J11" s="7" t="n"/>
       <c r="K11" s="7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>20000</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>55000</t>
-        </is>
-      </c>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>высокое давление Ру100; котельная</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Штуцерная прочая</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>Клапан предохранительный штуцерный сигнальный Ду6Ру100-250</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>524-03.188</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>новый</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I12" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" s="7" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="K12" s="7" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="inlineStr"/>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Котельная арматура — 7 позиций  28 шт по приложению  12 шт по факту  51 кг</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
+      <c r="K12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>высокое давление Ру100</t>
+          <t>высокое давление Ру100; котельная</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Стаканы переборочные</t>
+          <t>Штуцерная прочая</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>100</v>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Стакан переборочный Ду10Ру100</t>
+          <t>Клапан предохранительный штуцерный сигнальный Ду6 Ру100-230</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>554-35.265</t>
+          <t>524-35.2423-01</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -9181,49 +9107,53 @@
         </is>
       </c>
       <c r="H13" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="inlineStr"/>
+          <t>20000</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>55000</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>высокое давление Ру160</t>
+          <t>высокое давление Ру100; котельная</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Штуцерная угловая</t>
+          <t>Штуцерная прочая</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду10 Р160</t>
+          <t>Клапан предохранительный штуцерный сигнальный Ду6Ру100-250</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>522-03.149</t>
+          <t>524-03.188</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -9232,58 +9162,54 @@
         </is>
       </c>
       <c r="H14" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>0.7</v>
+        <v>2.06</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>4.2</v>
+        <v>4.12</v>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>15000</t>
-        </is>
-      </c>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>высокое давление Ру200</t>
+          <t>котельная</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Штуцерная угловая</t>
+          <t>Штуцерная прочая</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Клапан редукционный штуцерный угловой Ду10Ру200…30 с манометром</t>
+          <t>Клапан предохранительный штуцерный сигнальный Ду10Ру1,3-6,5</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>525-35.2634</t>
+          <t>524-03.174</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>б/у?</t>
+          <t>новый</t>
         </is>
       </c>
       <c r="H15" s="8" t="n">
@@ -9293,47 +9219,47 @@
         <v>1</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>7.5</v>
+        <v>0.77</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>7.5</v>
+        <v>0.77</v>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
           <t>15000</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>45000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>высокое давление Ру200</t>
+          <t>котельная</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Штуцерная угловая</t>
+          <t>Штуцерная прочая</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Клапан редукционный штуцерный угловой Ду10Ру200…30 с манометром</t>
+          <t>Клапан предохранительный штуцерный сигнальный Ду10Ру2,5-6,5</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>525-35.2634-04</t>
+          <t>524-03.173</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -9348,114 +9274,112 @@
         <v>1</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>7.5</v>
+        <v>1.24</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>7.5</v>
+        <v>1.24</v>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
           <t>15000</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>45000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>высокое давление Ру400</t>
+          <t>котельная</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Штуцерная проходная</t>
+          <t>Колонка смотровая</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>400</v>
+        <v>10</v>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру400</t>
+          <t>Колонка указательная с плоским рифленым стеклом Ду10Ру10</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>521-35.3238</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>новый</t>
-        </is>
-      </c>
+          <t>598-03.083-01</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr"/>
       <c r="H17" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="7" t="n">
-        <v>3.8</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I17" s="10" t="n"/>
+      <c r="J17" s="7" t="n"/>
       <c r="K17" s="7" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>65000</t>
+          <t>30000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>высокое давление Ру400</t>
+          <t>котельная</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Штуцерная проходная</t>
+          <t>Колонка смотровая</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>400</v>
+        <v>16</v>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру400</t>
+          <t>Клапан для колонки указательной Ду10 Ру16</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>521-03.420</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr"/>
+          <t>598-03.022-06</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>б/у</t>
+        </is>
+      </c>
       <c r="H18" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" s="10" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="I18" s="8" t="n">
+        <v>6</v>
+      </c>
       <c r="J18" s="7" t="n">
-        <v>3.64</v>
+        <v>1.5</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
@@ -9467,134 +9391,102 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>высокое давление Ру160</t>
+          <t>котельная</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Штуцерная угловая</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>160</v>
+        <v>10</v>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15 Ру160</t>
+          <t>Клапан паровой Ду65Ру10</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>521-03.387</t>
+          <t>581-03.034</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>новый</t>
+          <t>новый?</t>
         </is>
       </c>
       <c r="H19" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>4.3</v>
+        <v>32.6</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>17.2</v>
+        <v>32.6</v>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="inlineStr"/>
+          <t>50-60</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>120-160000</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>высокое давление Ру100</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Штуцерная угловая</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>Клапан штуцерный угловой Ду20 Ру100</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>521-01.468-05</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>б/у</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="M20" s="5" t="inlineStr">
-        <is>
-          <t>18000</t>
-        </is>
-      </c>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Воздушные высокого давления — 12 позиций  43 шт по приложению  41 шт по факту  399 кг</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="4" t="n"/>
+      <c r="K20" s="4" t="n"/>
+      <c r="L20" s="4" t="n"/>
+      <c r="M20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>высокое давление Ру100</t>
+          <t>воздух высокого давления Ру400</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Стаканы переборочные</t>
+          <t>Штуцерная прочая</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Стакан переборочный Ду20Ру100</t>
+          <t>Клапан для манометра штущерный  Ду3Ру400 новый</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>554-03.909-03</t>
+          <t>521-03.406</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -9603,16 +9495,16 @@
         </is>
       </c>
       <c r="H21" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>5.1</v>
+        <v>2.2</v>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
@@ -9624,28 +9516,28 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>высокое давление Ру100</t>
+          <t>воздух высокого давления Ру160</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Стаканы переборочные</t>
+          <t>Штуцерная угловая</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Стакан переборочный Ду20Ру100</t>
+          <t>Клапан штуцерный угловой Ду10 Р160</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>554-03.905-06</t>
+          <t>522-03.149</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -9654,104 +9546,108 @@
         </is>
       </c>
       <c r="H22" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>39</v>
+        <v>4.2</v>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="M22" s="5" t="inlineStr"/>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>высокое давление Ру125</t>
+          <t>воздух высокого давления Ру200</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Штуцерная угловая</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Клапан пусковой Ду20Ру125</t>
+          <t>Клапан редукционный штуцерный угловой Ду10Ру200…30 с манометром</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>587-03.080</t>
+          <t>525-35.2634</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>б/у</t>
+          <t>б/у?</t>
         </is>
       </c>
       <c r="H23" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>5.6</v>
+        <v>7.5</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>39.2</v>
+        <v>7.5</v>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>25000</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>45000-65000</t>
+          <t>45000</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>высокое давление Ру160</t>
+          <t>воздух высокого давления Ру200</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Штуцерная проходная</t>
+          <t>Штуцерная угловая</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Клапан невозвратный штуцерный проходной Ду20Ру160</t>
+          <t>Клапан редукционный штуцерный угловой Ду10Ру200…30 с манометром</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>522-03.089</t>
+          <t>525-35.2634-04</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -9766,43 +9662,47 @@
         <v>1</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="M24" s="5" t="inlineStr"/>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>высокое давление Ру160</t>
+          <t>воздух высокого давления Ру400</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Штуцерная угловая</t>
+          <t>Штуцерная проходная</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>160</v>
+        <v>400</v>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду20 Ру160</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру400</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>521-03.479</t>
+          <t>521-35.3238</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -9817,81 +9717,71 @@
         <v>1</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>22000</t>
+          <t>65000</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>высокое давление Ру400</t>
+          <t>воздух высокого давления Ру400</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Штуцерная проходная</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>400</v>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Клапан редукционный штуц.проход.односедельный Ду20Ру400 у входа</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру400</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>525-03.044</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>новый ?</t>
-        </is>
-      </c>
+          <t>521-03.420</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I26" s="8" t="n">
-        <v>9</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="I26" s="10" t="n"/>
       <c r="J26" s="7" t="n">
-        <v>27</v>
+        <v>3.64</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>35000</t>
-        </is>
-      </c>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>90-120000</t>
-        </is>
-      </c>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>высокое давление Ру100</t>
+          <t>воздух высокого давления Ру160</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -9900,19 +9790,19 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду25 Ру 100</t>
+          <t>Клапан штуцерный угловой Ду15 Ру160</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>521--35.3363</t>
+          <t>521-03.387</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -9921,104 +9811,104 @@
         </is>
       </c>
       <c r="H27" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>2.9</v>
+        <v>17.2</v>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>20000</t>
-        </is>
-      </c>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>высокое давление Ру100</t>
+          <t>воздух высокого давления Ру125</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Стаканы переборочные</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Стакан переборочный Ду25Ру100</t>
+          <t>Клапан пусковой Ду20Ру125</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>554-35.156</t>
+          <t>587-03.080</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>новый</t>
+          <t>б/у</t>
         </is>
       </c>
       <c r="H28" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>2.5</v>
+        <v>5.6</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>5</v>
+        <v>39.2</v>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="M28" s="5" t="inlineStr"/>
+          <t>25000</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>45000-65000</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>высокое давление Ру100</t>
+          <t>воздух высокого давления Ру160</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Штуцерная угловая</t>
+          <t>Штуцерная проходная</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32Ру100</t>
+          <t>Клапан невозвратный штуцерный проходной Ду20Ру160</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>521-01.468-07</t>
+          <t>522-03.089</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -10027,32 +9917,28 @@
         </is>
       </c>
       <c r="H29" s="8" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>102.3</v>
+        <v>2.3</v>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>6500</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>22000</t>
-        </is>
-      </c>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>высокое давление Ру100</t>
+          <t>воздух высокого давления Ру160</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -10061,19 +9947,19 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32Ру100</t>
+          <t>Клапан штуцерный угловой Ду20 Ру160</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>521-01.464-07</t>
+          <t>521-03.479</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -10082,20 +9968,20 @@
         </is>
       </c>
       <c r="H30" s="8" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>46.2</v>
+        <v>1.8</v>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>6500</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
@@ -10107,191 +9993,157 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>высокое давление Ру100</t>
+          <t>воздух высокого давления Ру400</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Штуцерная угловая</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32Ру100</t>
+          <t>Клапан редукционный штуц.проход.односедельный Ду20Ру400 у входа</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>521-01.464-06</t>
+          <t>525-03.044</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>новый</t>
+          <t>новый ?</t>
         </is>
       </c>
       <c r="H31" s="8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>3.3</v>
+        <v>27</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>3.3</v>
+        <v>243</v>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>6500</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>22000</t>
+          <t>90-120000</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>высокое давление Ру100</t>
+          <t>воздух высокого давления Ру125</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Штуцерная угловая</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
         <v>32</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32Ру100</t>
+          <t>Клапан пусковой Ду32Ру125</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>522-01.500-07</t>
+          <t>587-03.082</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>новый</t>
+          <t>б/у</t>
         </is>
       </c>
       <c r="H32" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>3.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>3.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>6500</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>22000</t>
+          <t>50000-70000</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>высокое давление Ру125</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>Прочее</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>125</v>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>Клапан пусковой Ду32Ру125</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>587-03.082</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>б/у</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="I33" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="J33" s="7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="K33" s="7" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="L33" s="5" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
-      </c>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>50000-70000</t>
-        </is>
-      </c>
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Клапаны высокого давления (Ру 100-150) — 10 позиций  159 шт по приложению  183 шт по факту  174 кг</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>высокое давление Ру150</t>
+          <t>высокое давление Ру100</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Штуцерная угловая</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="n"/>
+          <t>Штуцерная прочая</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>6</v>
+      </c>
       <c r="D34" s="5" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Рр150/10</t>
+          <t>Клапан для манометра штущерный сальниковый Ду6 Ру100 новый                                                                                                       (521-35.3434 -8 шт , 521-02.013 -86 шт , 521-35.3434-04 -30 шт)</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>521-ц22п</t>
+          <t>521-02.013</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -10300,46 +10152,82 @@
         </is>
       </c>
       <c r="H34" s="8" t="n">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>8</v>
+        <v>124</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>3000 - 4000</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>12000</t>
+          <t>14-17000</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>Котельная — 7 позиций, 12 шт</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="n"/>
-      <c r="C35" s="4" t="n"/>
-      <c r="D35" s="4" t="n"/>
-      <c r="E35" s="4" t="n"/>
-      <c r="F35" s="4" t="n"/>
-      <c r="G35" s="4" t="n"/>
-      <c r="H35" s="4" t="n"/>
-      <c r="I35" s="4" t="n"/>
-      <c r="J35" s="4" t="n"/>
-      <c r="K35" s="4" t="n"/>
-      <c r="L35" s="4" t="n"/>
-      <c r="M35" s="4" t="n"/>
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>высокое давление Ру100; котельная</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Штуцерная прочая</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>Клапан предохранительный штуцерный сигнальный Ду6 Ру100-230</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>524-35.2423-01</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K35" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>55000</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -10360,12 +10248,12 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Клапан предохранительный штуцерный сигнальный Ду6 Ру100-230</t>
+          <t>Клапан предохранительный штуцерный сигнальный Ду6Ру100-250</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>524-35.2423-01</t>
+          <t>524-03.188</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -10374,104 +10262,104 @@
         </is>
       </c>
       <c r="H36" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>3.5</v>
+        <v>2.06</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>3.5</v>
+        <v>4.12</v>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>20000</t>
-        </is>
-      </c>
-      <c r="M36" s="5" t="inlineStr">
-        <is>
-          <t>55000</t>
-        </is>
-      </c>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>высокое давление Ру100; котельная</t>
+          <t>высокое давление Ру100</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Штуцерная прочая</t>
+          <t>Штуцерная угловая</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D37" s="5" t="n">
         <v>100</v>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Клапан предохранительный штуцерный сигнальный Ду6Ру100-250</t>
+          <t>Клапан штуцерный угловой Ду20 Ру100</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>524-03.188</t>
+          <t>521-01.468-05</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>новый</t>
+          <t>б/у</t>
         </is>
       </c>
       <c r="H37" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J37" s="7" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="M37" s="5" t="inlineStr"/>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>18000</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>котельная</t>
+          <t>высокое давление Ру100</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Штуцерная прочая</t>
+          <t>Штуцерная угловая</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Клапан предохранительный штуцерный сигнальный Ду10Ру1,3-6,5</t>
+          <t>Клапан штуцерный угловой Ду25 Ру 100</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>524-03.174</t>
+          <t>521--35.3363</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -10486,47 +10374,47 @@
         <v>1</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>0.77</v>
+        <v>2.9</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>0.77</v>
+        <v>2.9</v>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>20000</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>котельная</t>
+          <t>высокое давление Ру100</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Штуцерная прочая</t>
+          <t>Штуцерная угловая</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Клапан предохранительный штуцерный сигнальный Ду10Ру2,5-6,5</t>
+          <t>Клапан штуцерный угловой Ду32Ру100</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>524-03.173</t>
+          <t>521-01.468-07</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -10535,156 +10423,168 @@
         </is>
       </c>
       <c r="H39" s="8" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="J39" s="7" t="n">
-        <v>1.24</v>
+        <v>3.3</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>1.24</v>
+        <v>102.3</v>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>22000</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>котельная</t>
+          <t>высокое давление Ру100</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Колонка смотровая</t>
+          <t>Штуцерная угловая</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Колонка указательная с плоским рифленым стеклом Ду10Ру10</t>
+          <t>Клапан штуцерный угловой Ду32Ру100</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>598-03.083-01</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr"/>
+          <t>521-01.464-07</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
       <c r="H40" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="I40" s="10" t="n"/>
-      <c r="J40" s="7" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="I40" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="J40" s="7" t="n">
+        <v>3.3</v>
+      </c>
       <c r="K40" s="7" t="n">
-        <v>0</v>
+        <v>46.2</v>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>12000</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>22000</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>котельная</t>
+          <t>высокое давление Ру100</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Колонка смотровая</t>
+          <t>Штуцерная угловая</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Клапан для колонки указательной Ду10 Ру16</t>
+          <t>Клапан штуцерный угловой Ду32Ру100</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>598-03.022-06</t>
+          <t>521-01.464-06</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>б/у</t>
+          <t>новый</t>
         </is>
       </c>
       <c r="H41" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J41" s="7" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>9</v>
+        <v>3.3</v>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="M41" s="5" t="inlineStr"/>
+          <t>6500</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>22000</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>котельная</t>
+          <t>высокое давление Ру100</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Штуцерная угловая</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Клапан паровой Ду65Ру10</t>
+          <t>Клапан штуцерный угловой Ду32Ру100</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>581-03.034</t>
+          <t>522-01.500-07</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>новый?</t>
+          <t>новый</t>
         </is>
       </c>
       <c r="H42" s="8" t="n">
@@ -10694,93 +10594,93 @@
         <v>1</v>
       </c>
       <c r="J42" s="7" t="n">
-        <v>32.6</v>
+        <v>3.3</v>
       </c>
       <c r="K42" s="7" t="n">
-        <v>32.6</v>
+        <v>3.3</v>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>50-60</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>120-160000</t>
+          <t>22000</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>Педальный — 2 позиций, 63 шт</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="n"/>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="4" t="n"/>
-      <c r="E43" s="4" t="n"/>
-      <c r="F43" s="4" t="n"/>
-      <c r="G43" s="4" t="n"/>
-      <c r="H43" s="4" t="n"/>
-      <c r="I43" s="4" t="n"/>
-      <c r="J43" s="4" t="n"/>
-      <c r="K43" s="4" t="n"/>
-      <c r="L43" s="4" t="n"/>
-      <c r="M43" s="4" t="n"/>
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>высокое давление Ру150</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Штуцерная угловая</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Рр150/10</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>521-ц22п</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I43" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="J43" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>педальный</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>Прочее</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>Клапан педальный Ду25</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>М528-03.001</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>б/у</t>
-        </is>
-      </c>
-      <c r="H44" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K44" s="7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L44" s="5" t="inlineStr">
-        <is>
-          <t>15000</t>
-        </is>
-      </c>
-      <c r="M44" s="5" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
-      </c>
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Педальные клапаны — 2 позиций  63 шт по приложению  63 шт по факту  346 кг</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n"/>
+      <c r="C44" s="4" t="n"/>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="n"/>
+      <c r="G44" s="4" t="n"/>
+      <c r="H44" s="4" t="n"/>
+      <c r="I44" s="4" t="n"/>
+      <c r="J44" s="4" t="n"/>
+      <c r="K44" s="4" t="n"/>
+      <c r="L44" s="4" t="n"/>
+      <c r="M44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -10799,7 +10699,7 @@
       <c r="D45" s="5" t="n"/>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Клапан педальный Ду25 новый приход</t>
+          <t>Клапан педальный Ду25</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
@@ -10809,185 +10709,84 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>новый</t>
+          <t>б/у</t>
         </is>
       </c>
       <c r="H45" s="8" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="J45" s="7" t="n">
         <v>5.5</v>
       </c>
       <c r="K45" s="7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>педальный</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="D46" s="5" t="n"/>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>Клапан педальный Ду25 новый приход</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>М528-03.001</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="I46" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="J46" s="7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K46" s="7" t="n">
         <v>341</v>
       </c>
-      <c r="L45" s="5" t="inlineStr">
+      <c r="L46" s="5" t="inlineStr">
         <is>
           <t>15000</t>
         </is>
       </c>
-      <c r="M45" s="5" t="inlineStr">
+      <c r="M46" s="5" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>Электромагнитный — 3 позиций, 2 шт</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="n"/>
-      <c r="C46" s="4" t="n"/>
-      <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="4" t="n"/>
-      <c r="G46" s="4" t="n"/>
-      <c r="H46" s="4" t="n"/>
-      <c r="I46" s="4" t="n"/>
-      <c r="J46" s="4" t="n"/>
-      <c r="K46" s="4" t="n"/>
-      <c r="L46" s="4" t="n"/>
-      <c r="M46" s="4" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>электромагнитный</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>Прочее</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>Клапан с электромагнитным ручным управлением Ду20/10 перем. 220В</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>587-35.8490-04</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>новый ?</t>
-        </is>
-      </c>
-      <c r="H47" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I47" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" s="7" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="K47" s="7" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="L47" s="5" t="inlineStr">
-        <is>
-          <t>25000</t>
-        </is>
-      </c>
-      <c r="M47" s="5" t="inlineStr">
-        <is>
-          <t>55000</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>электромагнитный</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>Прочее</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="n"/>
-      <c r="D48" s="5" t="n"/>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>Клапан с электромагнитным ручным управлением</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>587-182.126</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>новый</t>
-        </is>
-      </c>
-      <c r="H48" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I48" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="7" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="K48" s="7" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="L48" s="5" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="M48" s="5" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>электромагнитный</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>Прочее</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="n"/>
-      <c r="D49" s="5" t="n"/>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>Клапан фреоновый саленоидный</t>
-        </is>
-      </c>
-      <c r="F49" s="11" t="inlineStr"/>
-      <c r="G49" s="5" t="inlineStr"/>
-      <c r="H49" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I49" s="10" t="n"/>
-      <c r="J49" s="7" t="n"/>
-      <c r="K49" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="5" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="M49" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/marine_equipment/Остатки_Питер_по_группам.xlsx
+++ b/outputs/marine_equipment/Остатки_Питер_по_группам.xlsx
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Штуцерная угловая — 16 позиций  76 шт  202 кг</t>
+          <t>Штуцерная угловая — 16 позиций, 76 шт, 202 кг</t>
         </is>
       </c>
       <c r="B5" s="4" t="n"/>
@@ -1712,7 +1712,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Штуцерная проходная — 10 позиций  812 шт  997 кг</t>
+          <t>Штуцерная проходная — 10 позиций, 812 шт, 997 кг</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -2323,7 +2323,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Штуцерная  угол или проход не указан — 10 позиций  180 шт  184 кг</t>
+          <t>Штуцерная, угол или проход не указан — 10 позиций, 180 шт, 184 кг</t>
         </is>
       </c>
       <c r="B33" s="4" t="n"/>
@@ -2994,7 +2994,7 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Фланцевая угловая — 15 позиций  63 шт  1 187 кг</t>
+          <t>Фланцевая угловая — 15 позиций, 63 шт, 1 187 кг</t>
         </is>
       </c>
       <c r="B44" s="4" t="n"/>
@@ -3850,7 +3850,7 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Фланцевая проходная — 7 позиций  72 шт  1 521 кг</t>
+          <t>Фланцевая проходная — 7 позиций, 72 шт, 1 521 кг</t>
         </is>
       </c>
       <c r="B60" s="4" t="n"/>
@@ -4306,7 +4306,7 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Клинкеты — 4 позиций  48 шт  6 419 кг</t>
+          <t>Клинкеты — 4 позиций, 48 шт, 6 419 кг</t>
         </is>
       </c>
       <c r="B68" s="4" t="n"/>
@@ -4557,7 +4557,7 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Фильтры забортной воды — 7 позиций  21 шт  1 656 кг</t>
+          <t>Фильтры забортной воды — 7 позиций, 21 шт, 1 656 кг</t>
         </is>
       </c>
       <c r="B73" s="4" t="n"/>
@@ -4981,7 +4981,7 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Кингстоны — 5 позиций  7 шт  100 кг</t>
+          <t>Кингстоны — 5 позиций, 7 шт, 100 кг</t>
         </is>
       </c>
       <c r="B81" s="4" t="n"/>
@@ -5299,7 +5299,7 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>Головки вентиляционные — 7 позиций  43 шт  356 кг</t>
+          <t>Головки вентиляционные — 7 позиций, 43 шт, 356 кг</t>
         </is>
       </c>
       <c r="B87" s="4" t="n"/>
@@ -5717,7 +5717,7 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Колонка смотровая — 2 позиций  6 шт  9 кг</t>
+          <t>Колонка смотровая — 2 позиций, 6 шт, 9 кг</t>
         </is>
       </c>
       <c r="B95" s="4" t="n"/>
@@ -5860,7 +5860,7 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>Захлопки — 6 позиций  8 шт  171 кг</t>
+          <t>Захлопки — 6 позиций, 8 шт, 171 кг</t>
         </is>
       </c>
       <c r="B98" s="4" t="n"/>
@@ -6249,7 +6249,7 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>Коробки клапанные — 5 позиций  35 шт  1 886 кг</t>
+          <t>Коробки клапанные — 5 позиций, 35 шт, 1 886 кг</t>
         </is>
       </c>
       <c r="B105" s="4" t="n"/>
@@ -6569,7 +6569,7 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>Краны — 7 позиций  57 шт  44 кг</t>
+          <t>Краны — 7 позиций, 57 шт, 44 кг</t>
         </is>
       </c>
       <c r="B111" s="4" t="n"/>
@@ -7017,7 +7017,7 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>Стаканы переборочные — 4 позиций  36 шт  52 кг</t>
+          <t>Стаканы переборочные — 4 позиций, 36 шт, 52 кг</t>
         </is>
       </c>
       <c r="B119" s="4" t="n"/>
@@ -7276,7 +7276,7 @@
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>Пусковые клапаны — 2 позиций  15 шт  110 кг</t>
+          <t>Пусковые клапаны — 2 позиций, 15 шт, 110 кг</t>
         </is>
       </c>
       <c r="B124" s="4" t="n"/>
@@ -7433,7 +7433,7 @@
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>Редукционные клапаны — 3 позиций  11 шт  258 кг</t>
+          <t>Редукционные клапаны — 3 позиций, 11 шт, 258 кг</t>
         </is>
       </c>
       <c r="B127" s="4" t="n"/>
@@ -7661,7 +7661,7 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>Паровые клапаны — 1 позиций  1 шт  33 кг</t>
+          <t>Паровые клапаны — 1 позиций, 1 шт, 33 кг</t>
         </is>
       </c>
       <c r="B131" s="4" t="n"/>
@@ -7751,7 +7751,7 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>Электромагнитные клапаны — 3 позиций  2 шт  24 кг</t>
+          <t>Электромагнитные клапаны — 3 позиций, 2 шт, 24 кг</t>
         </is>
       </c>
       <c r="B133" s="4" t="n"/>
@@ -7943,7 +7943,7 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>Педальные клапаны — 2 позиций  63 шт  346 кг</t>
+          <t>Педальные клапаны — 2 позиций, 63 шт, 346 кг</t>
         </is>
       </c>
       <c r="B137" s="4" t="n"/>
@@ -8096,7 +8096,7 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>Эжекторы — 1 позиций  1 шт  4 кг</t>
+          <t>Эжекторы — 1 позиций, 1 шт, 4 кг</t>
         </is>
       </c>
       <c r="B140" s="4" t="n"/>
@@ -8170,7 +8170,7 @@
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>Без описания — уточнить — 2 позиций  4 шт  14 кг</t>
+          <t>Без описания — уточнить — 2 позиций, 4 шт, 14 кг</t>
         </is>
       </c>
       <c r="B142" s="4" t="n"/>
